--- a/data/trans_dic/P15B_tráfico-Clase-trans_dic.xlsx
+++ b/data/trans_dic/P15B_tráfico-Clase-trans_dic.xlsx
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>27,94%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,7 +684,7 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
-          <t>22,48%</t>
+          <t>22,85%</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -704,7 +704,7 @@
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>23,66%</t>
+          <t>25,38%</t>
         </is>
       </c>
     </row>
@@ -717,62 +717,62 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,23</t>
+          <t>0,0; 42,82</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>8,95; 45,65</t>
+          <t>9,13; 48,22</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>9,47; 49,8</t>
+          <t>9,38; 51,62</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>10,58; 47,6</t>
+          <t>13,05; 48,39</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,37</t>
+          <t>0,0; 56,09</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>11,7; 63,22</t>
+          <t>11,58; 62,53</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 22,4</t>
+          <t>0,0; 27,63</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>10,36; 37,81</t>
+          <t>12,58; 41,21</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,09</t>
+          <t>0,0; 31,8</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>14,25; 42,1</t>
+          <t>15,45; 43,17</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>6,44; 29,4</t>
+          <t>6,86; 30,83</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>13,86; 36,7</t>
+          <t>15,32; 37,51</t>
         </is>
       </c>
     </row>
@@ -804,7 +804,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>40,76%</t>
+          <t>37,92%</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -824,7 +824,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>32,6%</t>
+          <t>33,02%</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -844,7 +844,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>36,76%</t>
+          <t>35,51%</t>
         </is>
       </c>
     </row>
@@ -857,22 +857,22 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>8,05; 70,87</t>
+          <t>8,1; 68,73</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>20,71; 54,36</t>
+          <t>21,86; 54,49</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>10,66; 51,39</t>
+          <t>11,08; 53,49</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>20,65; 65,77</t>
+          <t>17,96; 61,17</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -882,37 +882,37 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>17,26; 55,31</t>
+          <t>15,58; 56,16</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>6,88; 44,95</t>
+          <t>7,03; 45,1</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>18,72; 49,13</t>
+          <t>17,75; 50,11</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>30,01; 78,3</t>
+          <t>31,96; 77,6</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>23,91; 50,08</t>
+          <t>23,65; 48,55</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>11,85; 39,94</t>
+          <t>11,54; 40,07</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>23,72; 52,37</t>
+          <t>23,3; 51,9</t>
         </is>
       </c>
     </row>
@@ -944,7 +944,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>36,93%</t>
+          <t>34,33%</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -964,7 +964,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>12,75%</t>
+          <t>13,7%</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>30,4%</t>
+          <t>28,97%</t>
         </is>
       </c>
     </row>
@@ -997,22 +997,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>2,75; 25,46</t>
+          <t>0,0; 21,27</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>16,74; 42,76</t>
+          <t>15,65; 40,71</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>3,31; 29,85</t>
+          <t>3,97; 33,01</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>22,79; 55,73</t>
+          <t>19,25; 52,33</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -1022,37 +1022,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>6,69; 50,92</t>
+          <t>6,77; 58,39</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>9,36; 66,64</t>
+          <t>9,17; 65,63</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>3,85; 33,36</t>
+          <t>0,0; 34,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,29; 18,64</t>
+          <t>2,27; 18,92</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>16,46; 38,85</t>
+          <t>16,11; 39,63</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>7,79; 33,09</t>
+          <t>7,53; 33,49</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>19,23; 44,41</t>
+          <t>18,48; 42,24</t>
         </is>
       </c>
     </row>
@@ -1084,7 +1084,7 @@
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>21,21%</t>
+          <t>23,09%</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>20,64%</t>
+          <t>20,27%</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1124,7 +1124,7 @@
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>20,96%</t>
+          <t>21,92%</t>
         </is>
       </c>
     </row>
@@ -1137,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>25,92; 57,93</t>
+          <t>26,17; 57,3</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>14,56; 31,4</t>
+          <t>13,59; 30,72</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>17,8; 42,19</t>
+          <t>17,1; 41,38</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11,3; 38,13</t>
+          <t>12,82; 37,13</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>11,42; 46,15</t>
+          <t>8,86; 44,98</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>10,08; 32,64</t>
+          <t>10,0; 33,76</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>14,12; 42,19</t>
+          <t>13,88; 41,86</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>11,81; 34,29</t>
+          <t>10,72; 34,12</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>23,13; 48,52</t>
+          <t>23,79; 48,8</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>15,2; 28,62</t>
+          <t>15,11; 28,86</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>18,12; 37,96</t>
+          <t>19,59; 37,69</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>14,06; 32,0</t>
+          <t>15,06; 32,56</t>
         </is>
       </c>
     </row>
@@ -1224,7 +1224,7 @@
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>16,86%</t>
+          <t>18,57%</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -1244,7 +1244,7 @@
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,81%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>18,58%</t>
+          <t>19,29%</t>
         </is>
       </c>
     </row>
@@ -1277,69 +1277,69 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>25,2; 83,36</t>
+          <t>25,9; 85,24</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>9,94; 40,36</t>
+          <t>10,11; 39,23</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>5,07; 27,3</t>
+          <t>5,12; 27,94</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>7,1; 33,34</t>
+          <t>7,3; 34,4</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>8,1; 40,7</t>
+          <t>8,02; 41,64</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>8,63; 26,97</t>
+          <t>7,15; 26,37</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>4,28; 23,37</t>
+          <t>4,24; 24,06</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>10,63; 36,28</t>
+          <t>11,16; 37,37</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>17,5; 49,86</t>
+          <t>19,53; 49,95</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>11,13; 26,5</t>
+          <t>11,18; 26,71</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>6,77; 21,57</t>
+          <t>6,92; 21,52</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>11,52; 30,42</t>
+          <t>11,39; 30,23</t>
         </is>
       </c>
     </row>
     <row r="14">
       <c r="A14" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B14" s="3" t="inlineStr">
@@ -1364,7 +1364,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>42,17%</t>
+          <t>40,18%</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1384,7 +1384,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,48%</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>25,61%</t>
+          <t>24,95%</t>
         </is>
       </c>
     </row>
@@ -1417,62 +1417,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>24,74; 75,37</t>
+          <t>25,6; 74,22</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>14,96; 49,96</t>
+          <t>14,52; 47,84</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>6,34; 31,67</t>
+          <t>6,36; 34,57</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 90,17</t>
+          <t>0,0; 81,24</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,98</t>
+          <t>0,0; 23,24</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>6,67; 20,57</t>
+          <t>6,49; 20,43</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>7,55; 26,29</t>
+          <t>6,98; 27,45</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>9,83; 38,41</t>
+          <t>9,56; 39,31</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>12,31; 38,4</t>
+          <t>12,53; 38,95</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>10,01; 23,16</t>
+          <t>10,21; 23,46</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>8,66; 25,29</t>
+          <t>9,07; 25,56</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>11,91; 46,61</t>
+          <t>12,34; 41,44</t>
         </is>
       </c>
     </row>
@@ -1504,7 +1504,7 @@
       </c>
       <c r="F16" s="2" t="inlineStr">
         <is>
-          <t>27,03%</t>
+          <t>27,34%</t>
         </is>
       </c>
       <c r="G16" s="2" t="inlineStr">
@@ -1524,7 +1524,7 @@
       </c>
       <c r="J16" s="2" t="inlineStr">
         <is>
-          <t>21,7%</t>
+          <t>21,76%</t>
         </is>
       </c>
       <c r="K16" s="2" t="inlineStr">
@@ -1544,7 +1544,7 @@
       </c>
       <c r="N16" s="2" t="inlineStr">
         <is>
-          <t>24,29%</t>
+          <t>24,5%</t>
         </is>
       </c>
     </row>
@@ -1557,62 +1557,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
-          <t>24,45; 41,8</t>
+          <t>24,23; 41,37</t>
         </is>
       </c>
       <c r="D17" s="2" t="inlineStr">
         <is>
-          <t>20,63; 31,13</t>
+          <t>20,01; 31,03</t>
         </is>
       </c>
       <c r="E17" s="2" t="inlineStr">
         <is>
-          <t>15,9; 27,73</t>
+          <t>15,98; 28,57</t>
         </is>
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>19,8; 35,66</t>
+          <t>21,36; 35,04</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
         <is>
-          <t>13,73; 29,85</t>
+          <t>13,58; 30,63</t>
         </is>
       </c>
       <c r="H17" s="2" t="inlineStr">
         <is>
-          <t>14,06; 24,24</t>
+          <t>13,89; 24,05</t>
         </is>
       </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
-          <t>12,32; 23,19</t>
+          <t>12,07; 23,1</t>
         </is>
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>16,49; 28,75</t>
+          <t>16,61; 28,54</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
         <is>
-          <t>21,77; 33,65</t>
+          <t>21,58; 33,46</t>
         </is>
       </c>
       <c r="L17" s="2" t="inlineStr">
         <is>
-          <t>18,81; 26,05</t>
+          <t>19,02; 26,6</t>
         </is>
       </c>
       <c r="M17" s="2" t="inlineStr">
         <is>
-          <t>15,52; 23,7</t>
+          <t>15,93; 23,57</t>
         </is>
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>20,29; 29,93</t>
+          <t>20,12; 29,57</t>
         </is>
       </c>
     </row>
@@ -1874,7 +1874,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>5910</t>
+          <t>7228</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1894,7 +1894,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>5218</t>
+          <t>5984</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1914,7 +1914,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>11129</t>
+          <t>13213</t>
         </is>
       </c>
     </row>
@@ -1927,62 +1927,62 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
-          <t>0; 5572</t>
+          <t>0; 5394</t>
         </is>
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>3039; 15504</t>
+          <t>3100; 16375</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>2039; 10724</t>
+          <t>2019; 11117</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>2521; 11347</t>
+          <t>3376; 12516</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
         <is>
-          <t>0; 3366</t>
+          <t>0; 4353</t>
         </is>
       </c>
       <c r="H6" s="2" t="inlineStr">
         <is>
-          <t>2027; 10955</t>
+          <t>2006; 10835</t>
         </is>
       </c>
       <c r="I6" s="2" t="inlineStr">
         <is>
-          <t>0; 4495</t>
+          <t>0; 5545</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>2405; 8776</t>
+          <t>3294; 10792</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>0; 6329</t>
+          <t>0; 6473</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>7307; 21594</t>
+          <t>7926; 22141</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>2677; 12231</t>
+          <t>2853; 12826</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>6520; 17265</t>
+          <t>7975; 19528</t>
         </is>
       </c>
     </row>
@@ -2082,7 +2082,7 @@
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>9841</t>
+          <t>9758</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2102,7 +2102,7 @@
       </c>
       <c r="J8" s="2" t="inlineStr">
         <is>
-          <t>7551</t>
+          <t>8248</t>
         </is>
       </c>
       <c r="K8" s="2" t="inlineStr">
@@ -2122,7 +2122,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>17392</t>
+          <t>18006</t>
         </is>
       </c>
     </row>
@@ -2135,22 +2135,22 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>1069; 9412</t>
+          <t>1076; 9128</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>6525; 17127</t>
+          <t>6888; 17166</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>1797; 8665</t>
+          <t>1868; 9019</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>4987; 15881</t>
+          <t>4621; 15739</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -2160,37 +2160,37 @@
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>4458; 14288</t>
+          <t>4025; 14506</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>1520; 9927</t>
+          <t>1552; 9961</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>4336; 11377</t>
+          <t>4435; 12519</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>5661; 14774</t>
+          <t>6030; 14641</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>13711; 28714</t>
+          <t>13558; 27840</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>4614; 15556</t>
+          <t>4493; 15605</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>11221; 24773</t>
+          <t>11815; 26320</t>
         </is>
       </c>
     </row>
@@ -2290,7 +2290,7 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>11970</t>
+          <t>12413</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -2310,7 +2310,7 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>1530</t>
+          <t>1738</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
@@ -2330,7 +2330,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>13500</t>
+          <t>14151</t>
         </is>
       </c>
     </row>
@@ -2343,22 +2343,22 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>777; 7200</t>
+          <t>0; 6017</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>10012; 25567</t>
+          <t>9357; 24341</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>1027; 9273</t>
+          <t>1234; 10255</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>7385; 18063</t>
+          <t>6962; 18924</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -2368,37 +2368,37 @@
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>1005; 7645</t>
+          <t>1017; 8766</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>934; 6654</t>
+          <t>916; 6553</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>462; 4003</t>
+          <t>0; 4361</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>760; 6197</t>
+          <t>756; 6289</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>12317; 29062</t>
+          <t>12053; 29646</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>3200; 13584</t>
+          <t>3092; 13750</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>8538; 19723</t>
+          <t>9026; 20632</t>
         </is>
       </c>
     </row>
@@ -2498,7 +2498,7 @@
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>14100</t>
+          <t>17961</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -2518,7 +2518,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>10215</t>
+          <t>11229</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2538,7 +2538,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>24315</t>
+          <t>29190</t>
         </is>
       </c>
     </row>
@@ -2551,62 +2551,62 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>10115; 22606</t>
+          <t>10212; 22361</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>13921; 30026</t>
+          <t>12997; 29374</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>10502; 24889</t>
+          <t>10088; 24409</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>7515; 25351</t>
+          <t>9974; 28883</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>2857; 11541</t>
+          <t>2215; 11249</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>4907; 15889</t>
+          <t>4869; 16436</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
         <is>
-          <t>5432; 16230</t>
+          <t>5338; 16103</t>
         </is>
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>5849; 16974</t>
+          <t>5936; 18899</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>14812; 31070</t>
+          <t>15233; 31246</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>21939; 41302</t>
+          <t>21808; 41646</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>17663; 36992</t>
+          <t>19094; 36731</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>16311; 37123</t>
+          <t>20057; 43367</t>
         </is>
       </c>
     </row>
@@ -2706,7 +2706,7 @@
       </c>
       <c r="F17" s="2" t="inlineStr">
         <is>
-          <t>6459</t>
+          <t>7489</t>
         </is>
       </c>
       <c r="G17" s="2" t="inlineStr">
@@ -2726,7 +2726,7 @@
       </c>
       <c r="J17" s="2" t="inlineStr">
         <is>
-          <t>10530</t>
+          <t>11281</t>
         </is>
       </c>
       <c r="K17" s="2" t="inlineStr">
@@ -2746,7 +2746,7 @@
       </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>16989</t>
+          <t>18770</t>
         </is>
       </c>
     </row>
@@ -2759,69 +2759,69 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>3186; 10538</t>
+          <t>3274; 10775</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>3903; 15845</t>
+          <t>3970; 15402</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>2068; 11133</t>
+          <t>2087; 11393</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>2720; 12771</t>
+          <t>2942; 13871</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>1819; 9135</t>
+          <t>1800; 9347</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>5024; 15706</t>
+          <t>4161; 15354</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>1731; 9443</t>
+          <t>1713; 9724</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>5649; 19272</t>
+          <t>6357; 21289</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6142; 17494</t>
+          <t>6852; 17526</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>10848; 25831</t>
+          <t>10902; 26044</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>5500; 17509</t>
+          <t>5620; 17470</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>10534; 27816</t>
+          <t>11081; 29412</t>
         </is>
       </c>
     </row>
     <row r="19">
       <c r="A19" s="1" t="inlineStr">
         <is>
-          <t>6.0</t>
+          <t>No ha trabajado</t>
         </is>
       </c>
       <c r="B19" s="3" t="inlineStr">
@@ -2914,7 +2914,7 @@
       </c>
       <c r="F20" s="2" t="inlineStr">
         <is>
-          <t>4946</t>
+          <t>4509</t>
         </is>
       </c>
       <c r="G20" s="2" t="inlineStr">
@@ -2934,7 +2934,7 @@
       </c>
       <c r="J20" s="2" t="inlineStr">
         <is>
-          <t>10004</t>
+          <t>10568</t>
         </is>
       </c>
       <c r="K20" s="2" t="inlineStr">
@@ -2954,7 +2954,7 @@
       </c>
       <c r="N20" s="2" t="inlineStr">
         <is>
-          <t>14950</t>
+          <t>15077</t>
         </is>
       </c>
     </row>
@@ -2967,62 +2967,62 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
-          <t>4005; 12203</t>
+          <t>4144; 12017</t>
         </is>
       </c>
       <c r="D21" s="2" t="inlineStr">
         <is>
-          <t>4013; 13402</t>
+          <t>3896; 12834</t>
         </is>
       </c>
       <c r="E21" s="2" t="inlineStr">
         <is>
-          <t>1810; 9038</t>
+          <t>1815; 9865</t>
         </is>
       </c>
       <c r="F21" s="2" t="inlineStr">
         <is>
-          <t>0; 10576</t>
+          <t>0; 9116</t>
         </is>
       </c>
       <c r="G21" s="2" t="inlineStr">
         <is>
-          <t>0; 7567</t>
+          <t>0; 6518</t>
         </is>
       </c>
       <c r="H21" s="2" t="inlineStr">
         <is>
-          <t>6022; 18581</t>
+          <t>5862; 18453</t>
         </is>
       </c>
       <c r="I21" s="2" t="inlineStr">
         <is>
-          <t>4565; 15888</t>
+          <t>4216; 16591</t>
         </is>
       </c>
       <c r="J21" s="2" t="inlineStr">
         <is>
-          <t>4583; 17917</t>
+          <t>4704; 19337</t>
         </is>
       </c>
       <c r="K21" s="2" t="inlineStr">
         <is>
-          <t>5445; 16984</t>
+          <t>5543; 17229</t>
         </is>
       </c>
       <c r="L21" s="2" t="inlineStr">
         <is>
-          <t>11728; 27133</t>
+          <t>11956; 27484</t>
         </is>
       </c>
       <c r="M21" s="2" t="inlineStr">
         <is>
-          <t>7705; 22505</t>
+          <t>8071; 22745</t>
         </is>
       </c>
       <c r="N21" s="2" t="inlineStr">
         <is>
-          <t>6953; 27207</t>
+          <t>7457; 25037</t>
         </is>
       </c>
     </row>
@@ -3122,7 +3122,7 @@
       </c>
       <c r="F23" s="2" t="inlineStr">
         <is>
-          <t>53226</t>
+          <t>59357</t>
         </is>
       </c>
       <c r="G23" s="2" t="inlineStr">
@@ -3142,7 +3142,7 @@
       </c>
       <c r="J23" s="2" t="inlineStr">
         <is>
-          <t>45048</t>
+          <t>49049</t>
         </is>
       </c>
       <c r="K23" s="2" t="inlineStr">
@@ -3162,7 +3162,7 @@
       </c>
       <c r="N23" s="2" t="inlineStr">
         <is>
-          <t>98274</t>
+          <t>108406</t>
         </is>
       </c>
     </row>
@@ -3175,62 +3175,62 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
-          <t>29837; 51001</t>
+          <t>29570; 50479</t>
         </is>
       </c>
       <c r="D24" s="2" t="inlineStr">
         <is>
-          <t>59210; 89346</t>
+          <t>57422; 89055</t>
         </is>
       </c>
       <c r="E24" s="2" t="inlineStr">
         <is>
-          <t>31443; 54840</t>
+          <t>31603; 56501</t>
         </is>
       </c>
       <c r="F24" s="2" t="inlineStr">
         <is>
-          <t>38981; 70218</t>
+          <t>46371; 76058</t>
         </is>
       </c>
       <c r="G24" s="2" t="inlineStr">
         <is>
-          <t>12875; 28002</t>
+          <t>12735; 28731</t>
         </is>
       </c>
       <c r="H24" s="2" t="inlineStr">
         <is>
-          <t>35916; 61910</t>
+          <t>35480; 61417</t>
         </is>
       </c>
       <c r="I24" s="2" t="inlineStr">
         <is>
-          <t>23578; 44404</t>
+          <t>23115; 44219</t>
         </is>
       </c>
       <c r="J24" s="2" t="inlineStr">
         <is>
-          <t>34234; 59698</t>
+          <t>37437; 64323</t>
         </is>
       </c>
       <c r="K24" s="2" t="inlineStr">
         <is>
-          <t>46981; 72619</t>
+          <t>46575; 72212</t>
         </is>
       </c>
       <c r="L24" s="2" t="inlineStr">
         <is>
-          <t>102019; 141291</t>
+          <t>103161; 144262</t>
         </is>
       </c>
       <c r="M24" s="2" t="inlineStr">
         <is>
-          <t>60415; 92239</t>
+          <t>61994; 91738</t>
         </is>
       </c>
       <c r="N24" s="2" t="inlineStr">
         <is>
-          <t>82080; 121098</t>
+          <t>89035; 130838</t>
         </is>
       </c>
     </row>
